--- a/wireframe/Sow-Tell-Wireframe.xlsx
+++ b/wireframe/Sow-Tell-Wireframe.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liene\bootcamp\Wizards-Inc\wireframe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA91A402-ABE6-4622-A40E-2CF1CC52981C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1092F02F-2AC4-43E1-80C3-7E53992AA80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FE77E57C-AFA9-426A-AC74-B78B50910902}"/>
   </bookViews>
   <sheets>
     <sheet name="Log-in page" sheetId="1" r:id="rId1"/>
-    <sheet name="Blog page" sheetId="2" r:id="rId2"/>
+    <sheet name="Post page" sheetId="2" r:id="rId2"/>
+    <sheet name="Account Page " sheetId="3" r:id="rId3"/>
+    <sheet name="Gallery" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,30 +38,150 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={8DC31F13-F672-44C8-B6F9-D563EA730BE1}</author>
+    <author>tc={CD64EC9D-F2C7-4DD6-8F96-79671E574420}</author>
+    <author>tc={719EAB06-00FA-4EDC-8383-4E592611310C}</author>
+  </authors>
+  <commentList>
+    <comment ref="A8" authorId="0" shapeId="0" xr:uid="{8DC31F13-F672-44C8-B6F9-D563EA730BE1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    If we are adding search function</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="1" shapeId="0" xr:uid="{CD64EC9D-F2C7-4DD6-8F96-79671E574420}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    I was thinking to make a ‘Gallery’ page. I will pull around 12 gardening images (3 x 4) and we could add that this would be ‘Instagram’ in ‘future development’ </t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="2" shapeId="0" xr:uid="{719EAB06-00FA-4EDC-8383-4E592611310C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Here they can change password, name.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={181AC72E-2984-427F-87CF-721E40FEF189}</author>
+    <author>tc={938A5A1D-7A96-40A2-AAFF-8115C01A9914}</author>
+    <author>tc={E2BE187B-232A-4FF5-B38F-66F1B388FC1F}</author>
+    <author>tc={EF871317-7E73-466B-B102-98197C5D2423}</author>
+    <author>tc={490AEA3B-1DE1-4B91-B676-11C1A705A591}</author>
+    <author>tc={7C0466DF-8140-47F0-B130-ED7BFABCAAD1}</author>
+  </authors>
+  <commentList>
+    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{181AC72E-2984-427F-87CF-721E40FEF189}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    This is unchangable</t>
+      </text>
+    </comment>
+    <comment ref="F6" authorId="1" shapeId="0" xr:uid="{938A5A1D-7A96-40A2-AAFF-8115C01A9914}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Add EDIT button</t>
+      </text>
+    </comment>
+    <comment ref="A8" authorId="2" shapeId="0" xr:uid="{E2BE187B-232A-4FF5-B38F-66F1B388FC1F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    If we are adding search function</t>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="3" shapeId="0" xr:uid="{EF871317-7E73-466B-B102-98197C5D2423}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Add EDFIT button</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="4" shapeId="0" xr:uid="{490AEA3B-1DE1-4B91-B676-11C1A705A591}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    I was thinking to make a ‘Gallery’ page. I will pull around 12 gardening images (3 x 4) and we could add that this would be ‘Instagram’ in ‘future development’ </t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="5" shapeId="0" xr:uid="{7C0466DF-8140-47F0-B130-ED7BFABCAAD1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Here they can change password, name.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={496B153C-231A-47D5-A256-B7A85524B07D}</author>
+    <author>tc={BC6C87D8-7510-46A0-B624-5BA262577BCC}</author>
+    <author>tc={2645E38A-363C-4790-8369-74001D9F0D7A}</author>
+  </authors>
+  <commentList>
+    <comment ref="A8" authorId="0" shapeId="0" xr:uid="{496B153C-231A-47D5-A256-B7A85524B07D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    If we are adding search function</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="1" shapeId="0" xr:uid="{BC6C87D8-7510-46A0-B624-5BA262577BCC}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    I was thinking to make a ‘Gallery’ page. I will pull around 12 gardening images (3 x 4) and we could add that this would be ‘Instagram’ in ‘future development’ </t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="2" shapeId="0" xr:uid="{2645E38A-363C-4790-8369-74001D9F0D7A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Here they can change password, name.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="48">
   <si>
     <t>Logo</t>
   </si>
   <si>
-    <t>Brand name</t>
-  </si>
-  <si>
-    <t>Sproutly</t>
-  </si>
-  <si>
-    <t>Rooted</t>
-  </si>
-  <si>
     <t>Sow &amp; Tell</t>
   </si>
   <si>
-    <t>Zest</t>
-  </si>
-  <si>
-    <t>Bloom-Share</t>
-  </si>
-  <si>
     <t>Register</t>
   </si>
   <si>
@@ -87,12 +209,6 @@
     <t>Logo (smaller version)</t>
   </si>
   <si>
-    <t>Home page</t>
-  </si>
-  <si>
-    <t>Blog</t>
-  </si>
-  <si>
     <t>username1</t>
   </si>
   <si>
@@ -109,13 +225,106 @@
   </si>
   <si>
     <t>username3</t>
+  </si>
+  <si>
+    <t>The social network for roots and shoots.</t>
+  </si>
+  <si>
+    <t>Share your garden's journey.</t>
+  </si>
+  <si>
+    <t>chooses category/ tag</t>
+  </si>
+  <si>
+    <t>CTA - Plant Your Post</t>
+  </si>
+  <si>
+    <t>Post1</t>
+  </si>
+  <si>
+    <t>Post2</t>
+  </si>
+  <si>
+    <t>Post3</t>
+  </si>
+  <si>
+    <t>Post4</t>
+  </si>
+  <si>
+    <t>User adds their post in here.</t>
+  </si>
+  <si>
+    <t>// this is a list of posts//</t>
+  </si>
+  <si>
+    <t>Nav Bar</t>
+  </si>
+  <si>
+    <t>Home Page</t>
+  </si>
+  <si>
+    <t>Search ???</t>
+  </si>
+  <si>
+    <t>Gallery</t>
+  </si>
+  <si>
+    <t>User account page</t>
+  </si>
+  <si>
+    <t>Username:</t>
+  </si>
+  <si>
+    <t>Name:</t>
+  </si>
+  <si>
+    <t>John Doe</t>
+  </si>
+  <si>
+    <t>greenfingers</t>
+  </si>
+  <si>
+    <t>Password:</t>
+  </si>
+  <si>
+    <t>pasw@1234</t>
+  </si>
+  <si>
+    <t>img1</t>
+  </si>
+  <si>
+    <t>img2</t>
+  </si>
+  <si>
+    <t>img3</t>
+  </si>
+  <si>
+    <t>img4</t>
+  </si>
+  <si>
+    <t>img5</t>
+  </si>
+  <si>
+    <t>img6</t>
+  </si>
+  <si>
+    <t>img7</t>
+  </si>
+  <si>
+    <t>img8</t>
+  </si>
+  <si>
+    <t>img9</t>
+  </si>
+  <si>
+    <t>A post a day keeps the aphids... well, it won't keep the aphids away, but at least you'll have someone to complain to about them.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,6 +347,45 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -147,7 +395,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -309,31 +557,128 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -352,39 +697,138 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -398,6 +842,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="liene klavina" id="{21BF80AD-7904-4FA1-8602-45F0B3EC668C}" userId="0440f43c4216b84b" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -715,382 +1165,2636 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A8" dT="2026-03-16T21:35:56.10" personId="{21BF80AD-7904-4FA1-8602-45F0B3EC668C}" id="{8DC31F13-F672-44C8-B6F9-D563EA730BE1}">
+    <text>If we are adding search function</text>
+  </threadedComment>
+  <threadedComment ref="A10" dT="2026-03-16T21:38:20.49" personId="{21BF80AD-7904-4FA1-8602-45F0B3EC668C}" id="{CD64EC9D-F2C7-4DD6-8F96-79671E574420}">
+    <text xml:space="preserve">I was thinking to make a ‘Gallery’ page. I will pull around 12 gardening images (3 x 4) and we could add that this would be ‘Instagram’ in ‘future development’ </text>
+  </threadedComment>
+  <threadedComment ref="A12" dT="2026-03-16T21:39:15.76" personId="{21BF80AD-7904-4FA1-8602-45F0B3EC668C}" id="{719EAB06-00FA-4EDC-8383-4E592611310C}">
+    <text>Here they can change password, name.</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="F4" dT="2026-03-16T21:41:10.34" personId="{21BF80AD-7904-4FA1-8602-45F0B3EC668C}" id="{181AC72E-2984-427F-87CF-721E40FEF189}">
+    <text>This is unchangable</text>
+  </threadedComment>
+  <threadedComment ref="F6" dT="2026-03-16T21:41:22.18" personId="{21BF80AD-7904-4FA1-8602-45F0B3EC668C}" id="{938A5A1D-7A96-40A2-AAFF-8115C01A9914}">
+    <text>Add EDIT button</text>
+  </threadedComment>
+  <threadedComment ref="A8" dT="2026-03-16T21:35:56.10" personId="{21BF80AD-7904-4FA1-8602-45F0B3EC668C}" id="{E2BE187B-232A-4FF5-B38F-66F1B388FC1F}">
+    <text>If we are adding search function</text>
+  </threadedComment>
+  <threadedComment ref="F8" dT="2026-03-16T21:42:35.97" personId="{21BF80AD-7904-4FA1-8602-45F0B3EC668C}" id="{EF871317-7E73-466B-B102-98197C5D2423}">
+    <text>Add EDFIT button</text>
+  </threadedComment>
+  <threadedComment ref="A10" dT="2026-03-16T21:38:20.49" personId="{21BF80AD-7904-4FA1-8602-45F0B3EC668C}" id="{490AEA3B-1DE1-4B91-B676-11C1A705A591}">
+    <text xml:space="preserve">I was thinking to make a ‘Gallery’ page. I will pull around 12 gardening images (3 x 4) and we could add that this would be ‘Instagram’ in ‘future development’ </text>
+  </threadedComment>
+  <threadedComment ref="A12" dT="2026-03-16T21:39:15.76" personId="{21BF80AD-7904-4FA1-8602-45F0B3EC668C}" id="{7C0466DF-8140-47F0-B130-ED7BFABCAAD1}">
+    <text>Here they can change password, name.</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A8" dT="2026-03-16T21:35:56.10" personId="{21BF80AD-7904-4FA1-8602-45F0B3EC668C}" id="{496B153C-231A-47D5-A256-B7A85524B07D}">
+    <text>If we are adding search function</text>
+  </threadedComment>
+  <threadedComment ref="A10" dT="2026-03-16T21:38:20.49" personId="{21BF80AD-7904-4FA1-8602-45F0B3EC668C}" id="{BC6C87D8-7510-46A0-B624-5BA262577BCC}">
+    <text xml:space="preserve">I was thinking to make a ‘Gallery’ page. I will pull around 12 gardening images (3 x 4) and we could add that this would be ‘Instagram’ in ‘future development’ </text>
+  </threadedComment>
+  <threadedComment ref="A12" dT="2026-03-16T21:39:15.76" personId="{21BF80AD-7904-4FA1-8602-45F0B3EC668C}" id="{2645E38A-363C-4790-8369-74001D9F0D7A}">
+    <text>Here they can change password, name.</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{733A0B9B-4DBE-40F6-98A1-542956D706FD}">
-  <dimension ref="C2:L27"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="4"/>
-      <c r="J3" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-    </row>
-    <row r="4" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C4" s="5"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C5" s="5"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="7"/>
-      <c r="K5" s="13" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="44"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="45"/>
+    </row>
+    <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="46"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="47"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="46"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="47"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="46"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="47"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="46"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="60" t="s">
+        <v>2</v>
+      </c>
+      <c r="L5" s="53"/>
+      <c r="M5" s="53"/>
+      <c r="N5" s="47"/>
+    </row>
+    <row r="6" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="46"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="53"/>
+      <c r="N6" s="47"/>
+    </row>
+    <row r="7" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="46"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="K7" s="19"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="53"/>
+      <c r="N7" s="47"/>
+    </row>
+    <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="46"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="65"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="53"/>
+      <c r="N8" s="47"/>
+    </row>
+    <row r="9" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="46"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="22"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="53"/>
+      <c r="N9" s="47"/>
+    </row>
+    <row r="10" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="46"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="53"/>
+      <c r="N10" s="47"/>
+    </row>
+    <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="46"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="K11" s="22"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="53"/>
+      <c r="N11" s="47"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="46"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="53"/>
+      <c r="N12" s="47"/>
+    </row>
+    <row r="13" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="46"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="53"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="53"/>
+      <c r="N13" s="47"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="46"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K14" s="13"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="53"/>
+      <c r="N14" s="47"/>
+    </row>
+    <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="46"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="53"/>
+      <c r="N15" s="47"/>
+    </row>
+    <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="46"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="53"/>
+      <c r="K16" s="53"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="53"/>
+      <c r="N16" s="47"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="46"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="53"/>
+      <c r="L17" s="53"/>
+      <c r="M17" s="53"/>
+      <c r="N17" s="47"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="46"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="53"/>
+      <c r="L18" s="53"/>
+      <c r="M18" s="53"/>
+      <c r="N18" s="47"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="46"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="53"/>
+      <c r="M19" s="53"/>
+      <c r="N19" s="47"/>
+    </row>
+    <row r="20" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="46"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="53"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="47"/>
+    </row>
+    <row r="21" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="46"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="22"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="47"/>
+    </row>
+    <row r="22" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="46"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="53"/>
+      <c r="M22" s="53"/>
+      <c r="N22" s="47"/>
+    </row>
+    <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="46"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="22"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="47"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="46"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="47"/>
+    </row>
+    <row r="25" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="46"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="47"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="46"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="12" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C6" s="5"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C7" s="5"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="J7" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="K7" s="15"/>
-      <c r="L7" s="16"/>
-    </row>
-    <row r="8" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="5"/>
-      <c r="D8" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="5"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="7"/>
-      <c r="J9" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="18"/>
-      <c r="L9" s="19"/>
-    </row>
-    <row r="10" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C10" s="5"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C11" s="5"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="7"/>
-      <c r="J11" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="K11" s="18"/>
-      <c r="L11" s="19"/>
-    </row>
-    <row r="12" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C12" s="5"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="5"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C14" s="5"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="7"/>
-      <c r="J14" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="K14" s="21"/>
-      <c r="L14" s="22"/>
-    </row>
-    <row r="15" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C15" s="5"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="7"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="25"/>
-    </row>
-    <row r="16" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C16" s="8"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="K19" s="26" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="3:12" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C20" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D20" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D21" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="K21" s="18"/>
-      <c r="L21" s="19"/>
-    </row>
-    <row r="22" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D23" t="s">
-        <v>5</v>
-      </c>
-      <c r="J23" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="K23" s="18"/>
-      <c r="L23" s="19"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="D24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="J26" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="K26" s="21"/>
-      <c r="L26" s="22"/>
-    </row>
-    <row r="27" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J27" s="23"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="25"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="47"/>
+    </row>
+    <row r="27" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="46"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="47"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="46"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="47"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="46"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="53"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="53"/>
+      <c r="M29" s="53"/>
+      <c r="N29" s="47"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="46"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="53"/>
+      <c r="M30" s="53"/>
+      <c r="N30" s="47"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="46"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="53"/>
+      <c r="M31" s="53"/>
+      <c r="N31" s="47"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="48"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="56"/>
+      <c r="E32" s="56"/>
+      <c r="F32" s="56"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="56"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="56"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="56"/>
+      <c r="N32" s="49"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="J26:L27"/>
+    <mergeCell ref="C20:F21"/>
+    <mergeCell ref="C22:F23"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="D8:E9"/>
     <mergeCell ref="J14:L15"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="J11:L11"/>
     <mergeCell ref="J9:L9"/>
-    <mergeCell ref="J21:L21"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="J26:L27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39184858-8DC0-4046-B941-100DAA15A86B}">
-  <dimension ref="B3:I24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39184858-8DC0-4046-B941-100DAA15A86B}">
+  <dimension ref="A1:N38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="45"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="46"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="47"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="46"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="47"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="69" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="47"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="46"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="53"/>
+      <c r="N5" s="47"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="53"/>
+      <c r="N6" s="47"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="46"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="53"/>
+      <c r="L7" s="53"/>
+      <c r="M7" s="53"/>
+      <c r="N7" s="47"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="53"/>
+      <c r="N8" s="47"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="46"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="53"/>
+      <c r="N9" s="47"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="59" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="59"/>
+      <c r="K10" s="59"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="53"/>
+      <c r="N10" s="47"/>
+    </row>
+    <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="46"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="53"/>
+      <c r="N11" s="47"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="29"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="53"/>
+      <c r="N12" s="47"/>
+    </row>
+    <row r="13" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="46"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="53"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="53"/>
+      <c r="N13" s="47"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="46"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="53"/>
+      <c r="M14" s="53"/>
+      <c r="N14" s="47"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="46"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="53"/>
+      <c r="M15" s="53"/>
+      <c r="N15" s="47"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="46"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="53"/>
+      <c r="K16" s="53"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="53"/>
+      <c r="N16" s="47"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="46"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="53"/>
+      <c r="M17" s="53"/>
+      <c r="N17" s="47"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="46"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="53"/>
+      <c r="M18" s="53"/>
+      <c r="N18" s="47"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="46"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
+      <c r="L19" s="53"/>
+      <c r="M19" s="53"/>
+      <c r="N19" s="47"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="46"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" s="10"/>
+      <c r="J20" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K20" s="10"/>
+      <c r="L20" s="53"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="47"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="46"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K21" s="10"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="47"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="46"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="53"/>
+      <c r="M22" s="53"/>
+      <c r="N22" s="47"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="46"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="53"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="47"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="46"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="47"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="46"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="10"/>
+      <c r="J25" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K25" s="10"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="47"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="46"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K26" s="10"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="47"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="46"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="47"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="46"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="53"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="47"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="46"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="53"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="53"/>
+      <c r="M29" s="53"/>
+      <c r="N29" s="47"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="46"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="10"/>
+      <c r="J30" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K30" s="10"/>
+      <c r="L30" s="53"/>
+      <c r="M30" s="53"/>
+      <c r="N30" s="47"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="46"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31" s="10"/>
+      <c r="L31" s="53"/>
+      <c r="M31" s="53"/>
+      <c r="N31" s="47"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="46"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="53"/>
+      <c r="M32" s="53"/>
+      <c r="N32" s="47"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="46"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="53"/>
+      <c r="N33" s="47"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="46"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="53"/>
+      <c r="N34" s="47"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="46"/>
+      <c r="B35" s="53"/>
+      <c r="C35" s="53"/>
+      <c r="D35" s="53"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="E4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="29"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="F8" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="29"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H9" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="29"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="29"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="F13" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="29"/>
-      <c r="H13" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="29"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H14" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" s="29"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="29"/>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="F18" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="29"/>
-      <c r="H18" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="I18" s="29"/>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="H19" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="I19" s="29"/>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="29"/>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="F23" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="29"/>
-      <c r="H23" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="I23" s="29"/>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="H24" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="I24" s="29"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K35" s="10"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="53"/>
+      <c r="N35" s="47"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="46"/>
+      <c r="B36" s="53"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K36" s="10"/>
+      <c r="L36" s="53"/>
+      <c r="M36" s="53"/>
+      <c r="N36" s="47"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="46"/>
+      <c r="B37" s="53"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="53"/>
+      <c r="N37" s="47"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="48"/>
+      <c r="B38" s="56"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="56"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="56"/>
+      <c r="K38" s="56"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="56"/>
+      <c r="N38" s="49"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="C16:I16"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="C21:I21"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="C11:I11"/>
+  <mergeCells count="27">
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="E18:K18"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="E23:K23"/>
+    <mergeCell ref="E17:K17"/>
+    <mergeCell ref="E2:K2"/>
+    <mergeCell ref="E8:K9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="G12:I13"/>
+    <mergeCell ref="E4:K5"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="E28:K28"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="E33:K33"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J31:K31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94F21E1-2632-4D0E-B85D-D7E8D192241E}">
+  <dimension ref="A1:N37"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="45"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="46"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="47"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="46"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="47"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="47"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="46"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="53"/>
+      <c r="N5" s="47"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="53"/>
+      <c r="N6" s="47"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="46"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="53"/>
+      <c r="L7" s="53"/>
+      <c r="M7" s="53"/>
+      <c r="N7" s="47"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="57" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="53"/>
+      <c r="N8" s="47"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="46"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="53"/>
+      <c r="K9" s="53"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="53"/>
+      <c r="N9" s="47"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="53"/>
+      <c r="N10" s="47"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="46"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="53"/>
+      <c r="N11" s="47"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="53"/>
+      <c r="N12" s="47"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="46"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="53"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="53"/>
+      <c r="N13" s="47"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="46"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="53"/>
+      <c r="M14" s="53"/>
+      <c r="N14" s="47"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="46"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="53"/>
+      <c r="M15" s="53"/>
+      <c r="N15" s="47"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="46"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="53"/>
+      <c r="K16" s="53"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="53"/>
+      <c r="N16" s="47"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="46"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="53"/>
+      <c r="L17" s="53"/>
+      <c r="M17" s="53"/>
+      <c r="N17" s="47"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="46"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="53"/>
+      <c r="L18" s="53"/>
+      <c r="M18" s="53"/>
+      <c r="N18" s="47"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="46"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
+      <c r="L19" s="53"/>
+      <c r="M19" s="53"/>
+      <c r="N19" s="47"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="46"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="53"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="47"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="46"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="47"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="46"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="53"/>
+      <c r="M22" s="53"/>
+      <c r="N22" s="47"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="46"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="53"/>
+      <c r="L23" s="53"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="47"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="46"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="47"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="46"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="47"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="46"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="47"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="46"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="47"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="46"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="47"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="46"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="53"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="53"/>
+      <c r="M29" s="53"/>
+      <c r="N29" s="47"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="46"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="53"/>
+      <c r="M30" s="53"/>
+      <c r="N30" s="47"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="46"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="53"/>
+      <c r="M31" s="53"/>
+      <c r="N31" s="47"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="46"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="53"/>
+      <c r="M32" s="53"/>
+      <c r="N32" s="47"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="46"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="53"/>
+      <c r="N33" s="47"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="46"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="53"/>
+      <c r="N34" s="47"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="46"/>
+      <c r="B35" s="53"/>
+      <c r="C35" s="53"/>
+      <c r="D35" s="53"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="53"/>
+      <c r="N35" s="47"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="46"/>
+      <c r="B36" s="53"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="53"/>
+      <c r="M36" s="53"/>
+      <c r="N36" s="47"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="48"/>
+      <c r="B37" s="56"/>
+      <c r="C37" s="56"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="56"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="56"/>
+      <c r="K37" s="56"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="56"/>
+      <c r="N37" s="49"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:B12"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F8" r:id="rId1" xr:uid="{AB0759F5-B436-4EC4-ABBD-3C96423C558C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA729801-4BBB-4D56-B2FD-D1C8269180A5}">
+  <dimension ref="A1:N39"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="45"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="46"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="47"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="46"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="54" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="47"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="47"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="46"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="53"/>
+      <c r="N5" s="47"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="35"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="35"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" s="35"/>
+      <c r="M6" s="53"/>
+      <c r="N6" s="47"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="46"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="50"/>
+      <c r="L7" s="51"/>
+      <c r="M7" s="53"/>
+      <c r="N7" s="47"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="50"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="53"/>
+      <c r="N8" s="47"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="46"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="53"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="53"/>
+      <c r="N9" s="47"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="53"/>
+      <c r="N10" s="47"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="46"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="53"/>
+      <c r="N11" s="47"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="35"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="35"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="L12" s="35"/>
+      <c r="M12" s="53"/>
+      <c r="N12" s="47"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="46"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="51"/>
+      <c r="M13" s="53"/>
+      <c r="N13" s="47"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="46"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="50"/>
+      <c r="L14" s="51"/>
+      <c r="M14" s="53"/>
+      <c r="N14" s="47"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="46"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="37"/>
+      <c r="M15" s="53"/>
+      <c r="N15" s="47"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="46"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="53"/>
+      <c r="K16" s="53"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="53"/>
+      <c r="N16" s="47"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="46"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="53"/>
+      <c r="L17" s="53"/>
+      <c r="M17" s="53"/>
+      <c r="N17" s="47"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="46"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="35"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" s="35"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="L18" s="35"/>
+      <c r="M18" s="53"/>
+      <c r="N18" s="47"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="46"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="50"/>
+      <c r="L19" s="51"/>
+      <c r="M19" s="53"/>
+      <c r="N19" s="47"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="46"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="50"/>
+      <c r="L20" s="51"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="47"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="46"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="47"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="46"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="53"/>
+      <c r="M22" s="53"/>
+      <c r="N22" s="47"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="46"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="53"/>
+      <c r="L23" s="53"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="47"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="46"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="47"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="46"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="47"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="46"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="47"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="46"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="47"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="46"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="47"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="46"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="53"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="53"/>
+      <c r="M29" s="53"/>
+      <c r="N29" s="47"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="46"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="53"/>
+      <c r="M30" s="53"/>
+      <c r="N30" s="47"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="46"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="53"/>
+      <c r="M31" s="53"/>
+      <c r="N31" s="47"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="46"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="53"/>
+      <c r="M32" s="53"/>
+      <c r="N32" s="47"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="46"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="53"/>
+      <c r="N33" s="47"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="46"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="53"/>
+      <c r="N34" s="47"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="46"/>
+      <c r="B35" s="53"/>
+      <c r="C35" s="53"/>
+      <c r="D35" s="53"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="53"/>
+      <c r="N35" s="47"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="46"/>
+      <c r="B36" s="53"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="53"/>
+      <c r="M36" s="53"/>
+      <c r="N36" s="47"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="46"/>
+      <c r="B37" s="53"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="53"/>
+      <c r="N37" s="47"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="46"/>
+      <c r="B38" s="53"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="53"/>
+      <c r="L38" s="53"/>
+      <c r="M38" s="53"/>
+      <c r="N38" s="47"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="48"/>
+      <c r="B39" s="56"/>
+      <c r="C39" s="56"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="56"/>
+      <c r="J39" s="56"/>
+      <c r="K39" s="56"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="56"/>
+      <c r="N39" s="49"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="K6:L9"/>
+    <mergeCell ref="E12:F15"/>
+    <mergeCell ref="H12:I15"/>
+    <mergeCell ref="K12:L15"/>
+    <mergeCell ref="E18:F21"/>
+    <mergeCell ref="H18:I21"/>
+    <mergeCell ref="K18:L21"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="E6:F9"/>
+    <mergeCell ref="H6:I9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/wireframe/Sow-Tell-Wireframe.xlsx
+++ b/wireframe/Sow-Tell-Wireframe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liene\bootcamp\Wizards-Inc\wireframe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD95A21-CD97-4D9D-8A7F-202E2FFB6BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C49B133-5DF0-43D0-BAF3-EC419B9613E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE77E57C-AFA9-426A-AC74-B78B50910902}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{FE77E57C-AFA9-426A-AC74-B78B50910902}"/>
   </bookViews>
   <sheets>
     <sheet name="Log-in page" sheetId="1" r:id="rId1"/>
@@ -278,9 +278,6 @@
     <t>Name:</t>
   </si>
   <si>
-    <t>John Doe</t>
-  </si>
-  <si>
     <t>greenfingers</t>
   </si>
   <si>
@@ -321,6 +318,9 @@
   </si>
   <si>
     <t>Join a community of growers sharing daily wins, garden fails, and everything in between.</t>
+  </si>
+  <si>
+    <t>First Name, Last Name</t>
   </si>
 </sst>
 </file>
@@ -666,139 +666,145 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
@@ -818,12 +824,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1246,11 +1246,11 @@
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="3"/>
-      <c r="J3" s="59" t="s">
+      <c r="J3" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="59"/>
-      <c r="L3" s="59"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
       <c r="N3" s="12"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -1278,34 +1278,34 @@
       <c r="A7" s="11"/>
       <c r="C7" s="4"/>
       <c r="F7" s="5"/>
-      <c r="J7" s="64" t="s">
+      <c r="J7" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="65"/>
-      <c r="L7" s="66"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="35"/>
       <c r="N7" s="12"/>
     </row>
     <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11"/>
       <c r="C8" s="4"/>
-      <c r="D8" s="60" t="s">
+      <c r="D8" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="E8" s="61"/>
+      <c r="E8" s="24"/>
       <c r="F8" s="5"/>
       <c r="N8" s="12"/>
     </row>
     <row r="9" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="62"/>
-      <c r="E9" s="63"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
       <c r="F9" s="5"/>
-      <c r="J9" s="48" t="s">
+      <c r="J9" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="K9" s="49"/>
-      <c r="L9" s="50"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="38"/>
       <c r="N9" s="12"/>
     </row>
     <row r="10" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1318,11 +1318,11 @@
       <c r="A11" s="11"/>
       <c r="C11" s="4"/>
       <c r="F11" s="5"/>
-      <c r="J11" s="48" t="s">
+      <c r="J11" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="K11" s="49"/>
-      <c r="L11" s="50"/>
+      <c r="K11" s="37"/>
+      <c r="L11" s="38"/>
       <c r="N11" s="12"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1341,20 +1341,20 @@
       <c r="A14" s="11"/>
       <c r="C14" s="4"/>
       <c r="F14" s="5"/>
-      <c r="J14" s="51" t="s">
+      <c r="J14" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="K14" s="52"/>
-      <c r="L14" s="53"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="29"/>
       <c r="N14" s="12"/>
     </row>
     <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11"/>
       <c r="C15" s="4"/>
       <c r="F15" s="5"/>
-      <c r="J15" s="54"/>
-      <c r="K15" s="55"/>
-      <c r="L15" s="56"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="32"/>
       <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1382,48 +1382,48 @@
     </row>
     <row r="20" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11"/>
-      <c r="C20" s="57" t="s">
+      <c r="C20" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
       <c r="N20" s="12"/>
     </row>
     <row r="21" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11"/>
-      <c r="C21" s="57"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
-      <c r="J21" s="48" t="s">
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="J21" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="K21" s="49"/>
-      <c r="L21" s="50"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="38"/>
       <c r="N21" s="12"/>
     </row>
     <row r="22" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11"/>
-      <c r="C22" s="58" t="s">
+      <c r="C22" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
       <c r="N22" s="12"/>
     </row>
     <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
-      <c r="J23" s="48" t="s">
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="J23" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="K23" s="49"/>
-      <c r="L23" s="50"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="38"/>
       <c r="N23" s="12"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1432,36 +1432,36 @@
     </row>
     <row r="25" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11"/>
-      <c r="C25" s="74" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="74"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
+      <c r="C25" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
       <c r="N25" s="12"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="11"/>
-      <c r="C26" s="74"/>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="J26" s="51" t="s">
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="J26" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="K26" s="52"/>
-      <c r="L26" s="53"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="29"/>
       <c r="N26" s="12"/>
     </row>
     <row r="27" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11"/>
-      <c r="C27" s="74"/>
-      <c r="D27" s="74"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="74"/>
-      <c r="J27" s="54"/>
-      <c r="K27" s="55"/>
-      <c r="L27" s="56"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="32"/>
       <c r="N27" s="12"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -1498,18 +1498,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="J26:L27"/>
+    <mergeCell ref="C20:F21"/>
+    <mergeCell ref="C22:F23"/>
+    <mergeCell ref="C25:F27"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="D8:E9"/>
     <mergeCell ref="J14:L15"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="J11:L11"/>
     <mergeCell ref="J9:L9"/>
-    <mergeCell ref="J21:L21"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="J26:L27"/>
-    <mergeCell ref="C20:F21"/>
-    <mergeCell ref="C22:F23"/>
-    <mergeCell ref="C25:F27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1540,15 +1540,15 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="28"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="47"/>
       <c r="N2" s="12"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -1556,38 +1556,38 @@
       <c r="N3" s="12"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="24"/>
-      <c r="E4" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="44"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="43"/>
+      <c r="E4" s="61" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="12"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="47"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="12"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="43"/>
       <c r="N6" s="12"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1598,45 +1598,45 @@
       <c r="N7" s="12"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="24"/>
+      <c r="B8" s="43"/>
       <c r="C8" s="17"/>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="31"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="50"/>
       <c r="N8" s="12"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="34"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
+      <c r="K9" s="53"/>
       <c r="N9" s="12"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="24"/>
+      <c r="B10" s="43"/>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
-      <c r="I10" s="35" t="s">
+      <c r="I10" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
       <c r="N10" s="12"/>
     </row>
     <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1647,22 +1647,22 @@
       <c r="N11" s="12"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="24"/>
-      <c r="G12" s="36" t="s">
+      <c r="B12" s="43"/>
+      <c r="G12" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="37"/>
-      <c r="I12" s="38"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="57"/>
       <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="41"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="60"/>
       <c r="N13" s="12"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1688,28 +1688,28 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="11"/>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="67"/>
+      <c r="H17" s="67"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="67"/>
+      <c r="K17" s="67"/>
       <c r="N17" s="12"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="24"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="43"/>
       <c r="N18" s="12"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1718,22 +1718,22 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="11"/>
-      <c r="H20" s="22" t="s">
+      <c r="H20" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="I20" s="24"/>
-      <c r="J20" s="22" t="s">
+      <c r="I20" s="43"/>
+      <c r="J20" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="K20" s="24"/>
+      <c r="K20" s="43"/>
       <c r="N20" s="12"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="11"/>
-      <c r="J21" s="22" t="s">
+      <c r="J21" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="24"/>
+      <c r="K21" s="43"/>
       <c r="N21" s="12"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1742,15 +1742,15 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="11"/>
-      <c r="E23" s="22" t="s">
+      <c r="E23" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="24"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="43"/>
       <c r="N23" s="12"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1759,22 +1759,22 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="11"/>
-      <c r="H25" s="22" t="s">
+      <c r="H25" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="I25" s="24"/>
-      <c r="J25" s="22" t="s">
+      <c r="I25" s="43"/>
+      <c r="J25" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="K25" s="24"/>
+      <c r="K25" s="43"/>
       <c r="N25" s="12"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="11"/>
-      <c r="J26" s="22" t="s">
+      <c r="J26" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="K26" s="24"/>
+      <c r="K26" s="43"/>
       <c r="N26" s="12"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -1783,15 +1783,15 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
-      <c r="E28" s="22" t="s">
+      <c r="E28" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="24"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="43"/>
       <c r="N28" s="12"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -1800,22 +1800,22 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="11"/>
-      <c r="H30" s="22" t="s">
+      <c r="H30" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="I30" s="24"/>
-      <c r="J30" s="22" t="s">
+      <c r="I30" s="43"/>
+      <c r="J30" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="K30" s="24"/>
+      <c r="K30" s="43"/>
       <c r="N30" s="12"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="11"/>
-      <c r="J31" s="22" t="s">
+      <c r="J31" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="K31" s="24"/>
+      <c r="K31" s="43"/>
       <c r="N31" s="12"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -1824,15 +1824,15 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="11"/>
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="24"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="44"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="43"/>
       <c r="N33" s="12"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -1841,22 +1841,22 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="11"/>
-      <c r="H35" s="22" t="s">
+      <c r="H35" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="I35" s="24"/>
-      <c r="J35" s="22" t="s">
+      <c r="I35" s="43"/>
+      <c r="J35" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="K35" s="24"/>
+      <c r="K35" s="43"/>
       <c r="N35" s="12"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="11"/>
-      <c r="J36" s="22" t="s">
+      <c r="J36" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="K36" s="24"/>
+      <c r="K36" s="43"/>
       <c r="N36" s="12"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
@@ -1881,6 +1881,22 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="E18:K18"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="E23:K23"/>
+    <mergeCell ref="E17:K17"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="E2:K2"/>
+    <mergeCell ref="E8:K9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="G12:I13"/>
+    <mergeCell ref="E4:K5"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="H25:I25"/>
     <mergeCell ref="J25:K25"/>
@@ -1892,22 +1908,6 @@
     <mergeCell ref="J35:K35"/>
     <mergeCell ref="J26:K26"/>
     <mergeCell ref="J31:K31"/>
-    <mergeCell ref="E2:K2"/>
-    <mergeCell ref="E8:K9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="G12:I13"/>
-    <mergeCell ref="E4:K5"/>
-    <mergeCell ref="E18:K18"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="E23:K23"/>
-    <mergeCell ref="E17:K17"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -1950,16 +1950,16 @@
       <c r="N3" s="12"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="24"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="43"/>
       <c r="E4" t="s">
         <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N4" s="12"/>
     </row>
@@ -1968,16 +1968,17 @@
       <c r="N5" s="12"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="43"/>
       <c r="E6" t="s">
         <v>33</v>
       </c>
-      <c r="F6" t="s">
-        <v>34</v>
-      </c>
+      <c r="F6" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="68"/>
       <c r="N6" s="12"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1985,16 +1986,16 @@
       <c r="N7" s="12"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="24"/>
+      <c r="B8" s="43"/>
       <c r="C8" s="17"/>
       <c r="E8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="19" t="s">
         <v>36</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>37</v>
       </c>
       <c r="N8" s="12"/>
     </row>
@@ -2003,10 +2004,10 @@
       <c r="N9" s="12"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="24"/>
+      <c r="B10" s="43"/>
       <c r="N10" s="12"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -2014,10 +2015,10 @@
       <c r="N11" s="12"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="24"/>
+      <c r="B12" s="43"/>
       <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -2133,7 +2134,8 @@
       <c r="N37" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="F6:G6"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A8:B8"/>
@@ -2177,19 +2179,19 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
-      <c r="G3" s="73" t="s">
+      <c r="G3" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
       <c r="N3" s="12"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="24"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="43"/>
       <c r="N4" s="12"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -2197,63 +2199,63 @@
       <c r="N5" s="12"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="E6" s="67" t="s">
+      <c r="B6" s="43"/>
+      <c r="E6" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="70"/>
+      <c r="H6" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="68"/>
-      <c r="H6" s="67" t="s">
+      <c r="I6" s="70"/>
+      <c r="K6" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="68"/>
-      <c r="K6" s="67" t="s">
-        <v>40</v>
-      </c>
-      <c r="L6" s="68"/>
+      <c r="L6" s="70"/>
       <c r="N6" s="12"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="70"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="70"/>
-      <c r="K7" s="69"/>
-      <c r="L7" s="70"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="72"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="72"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="72"/>
       <c r="N7" s="12"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="24"/>
+      <c r="B8" s="43"/>
       <c r="C8" s="17"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="70"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="70"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="70"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="72"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="72"/>
+      <c r="K8" s="71"/>
+      <c r="L8" s="72"/>
       <c r="N8" s="12"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="72"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="72"/>
-      <c r="K9" s="71"/>
-      <c r="L9" s="72"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="74"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="74"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="74"/>
       <c r="N9" s="12"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="24"/>
+      <c r="B10" s="43"/>
       <c r="N10" s="12"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -2261,52 +2263,52 @@
       <c r="N11" s="12"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="24"/>
-      <c r="E12" s="67" t="s">
+      <c r="B12" s="43"/>
+      <c r="E12" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="70"/>
+      <c r="H12" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="68"/>
-      <c r="H12" s="67" t="s">
+      <c r="I12" s="70"/>
+      <c r="K12" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="I12" s="68"/>
-      <c r="K12" s="67" t="s">
-        <v>43</v>
-      </c>
-      <c r="L12" s="68"/>
+      <c r="L12" s="70"/>
       <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="11"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="70"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="70"/>
-      <c r="K13" s="69"/>
-      <c r="L13" s="70"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="72"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="72"/>
+      <c r="K13" s="71"/>
+      <c r="L13" s="72"/>
       <c r="N13" s="12"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="11"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="70"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="70"/>
-      <c r="K14" s="69"/>
-      <c r="L14" s="70"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="72"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="72"/>
+      <c r="K14" s="71"/>
+      <c r="L14" s="72"/>
       <c r="N14" s="12"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="11"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="72"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="72"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="72"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="74"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="74"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="74"/>
       <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -2319,48 +2321,48 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="E18" s="67" t="s">
+      <c r="E18" s="69" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="70"/>
+      <c r="H18" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="F18" s="68"/>
-      <c r="H18" s="67" t="s">
+      <c r="I18" s="70"/>
+      <c r="K18" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="I18" s="68"/>
-      <c r="K18" s="67" t="s">
-        <v>46</v>
-      </c>
-      <c r="L18" s="68"/>
+      <c r="L18" s="70"/>
       <c r="N18" s="12"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="70"/>
-      <c r="H19" s="69"/>
-      <c r="I19" s="70"/>
-      <c r="K19" s="69"/>
-      <c r="L19" s="70"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="72"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="72"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="72"/>
       <c r="N19" s="12"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="11"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="70"/>
-      <c r="H20" s="69"/>
-      <c r="I20" s="70"/>
-      <c r="K20" s="69"/>
-      <c r="L20" s="70"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="72"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="72"/>
+      <c r="K20" s="71"/>
+      <c r="L20" s="72"/>
       <c r="N20" s="12"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="11"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="72"/>
-      <c r="H21" s="71"/>
-      <c r="I21" s="72"/>
-      <c r="K21" s="71"/>
-      <c r="L21" s="72"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="74"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="74"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="74"/>
       <c r="N21" s="12"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -2449,21 +2451,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="E18:F21"/>
+    <mergeCell ref="H18:I21"/>
+    <mergeCell ref="K18:L21"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="K6:L9"/>
+    <mergeCell ref="E12:F15"/>
+    <mergeCell ref="H12:I15"/>
+    <mergeCell ref="K12:L15"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="E6:F9"/>
     <mergeCell ref="H6:I9"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="K6:L9"/>
-    <mergeCell ref="E12:F15"/>
-    <mergeCell ref="H12:I15"/>
-    <mergeCell ref="K12:L15"/>
-    <mergeCell ref="E18:F21"/>
-    <mergeCell ref="H18:I21"/>
-    <mergeCell ref="K18:L21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/wireframe/Sow-Tell-Wireframe.xlsx
+++ b/wireframe/Sow-Tell-Wireframe.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liene\bootcamp\Wizards-Inc\wireframe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C49B133-5DF0-43D0-BAF3-EC419B9613E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7263860-E376-473A-942E-150B726A90CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{FE77E57C-AFA9-426A-AC74-B78B50910902}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{FE77E57C-AFA9-426A-AC74-B78B50910902}"/>
   </bookViews>
   <sheets>
-    <sheet name="Log-in page" sheetId="1" r:id="rId1"/>
+    <sheet name="Log-in  register page" sheetId="1" r:id="rId1"/>
     <sheet name="Post page" sheetId="2" r:id="rId2"/>
     <sheet name="Account Page " sheetId="3" r:id="rId3"/>
-    <sheet name="Gallery" sheetId="4" r:id="rId4"/>
+    <sheet name="About Us" sheetId="5" r:id="rId4"/>
+    <sheet name="Gallery" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,11 +43,11 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={8DC31F13-F672-44C8-B6F9-D563EA730BE1}</author>
+    <author>tc={719EAB06-00FA-4EDC-8383-4E592611310C}</author>
     <author>tc={CD64EC9D-F2C7-4DD6-8F96-79671E574420}</author>
-    <author>tc={719EAB06-00FA-4EDC-8383-4E592611310C}</author>
   </authors>
   <commentList>
-    <comment ref="A8" authorId="0" shapeId="0" xr:uid="{8DC31F13-F672-44C8-B6F9-D563EA730BE1}">
+    <comment ref="A11" authorId="0" shapeId="0" xr:uid="{8DC31F13-F672-44C8-B6F9-D563EA730BE1}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -54,20 +55,20 @@
     If we are adding search function</t>
       </text>
     </comment>
-    <comment ref="A10" authorId="1" shapeId="0" xr:uid="{CD64EC9D-F2C7-4DD6-8F96-79671E574420}">
+    <comment ref="A13" authorId="1" shapeId="0" xr:uid="{719EAB06-00FA-4EDC-8383-4E592611310C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Here they can change password, name.</t>
+      </text>
+    </comment>
+    <comment ref="A15" authorId="2" shapeId="0" xr:uid="{CD64EC9D-F2C7-4DD6-8F96-79671E574420}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     I was thinking to make a ‘Gallery’ page. I will pull around 12 gardening images (3 x 4) and we could add that this would be ‘Instagram’ in ‘future development’ </t>
-      </text>
-    </comment>
-    <comment ref="A12" authorId="2" shapeId="0" xr:uid="{719EAB06-00FA-4EDC-8383-4E592611310C}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Here they can change password, name.</t>
       </text>
     </comment>
   </commentList>
@@ -174,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
   <si>
     <t>Logo</t>
   </si>
@@ -251,9 +252,6 @@
     <t>Post4</t>
   </si>
   <si>
-    <t>User adds their post in here.</t>
-  </si>
-  <si>
     <t>// this is a list of posts//</t>
   </si>
   <si>
@@ -321,6 +319,33 @@
   </si>
   <si>
     <t>First Name, Last Name</t>
+  </si>
+  <si>
+    <t>Log-in if you would like to post.</t>
+  </si>
+  <si>
+    <t>email:</t>
+  </si>
+  <si>
+    <t>test@example.com</t>
+  </si>
+  <si>
+    <t>Blog List -posts owned by user.</t>
+  </si>
+  <si>
+    <t>Log-out</t>
+  </si>
+  <si>
+    <t>contact details:</t>
+  </si>
+  <si>
+    <t>header</t>
+  </si>
+  <si>
+    <t>footer</t>
+  </si>
+  <si>
+    <t>Footer</t>
   </si>
 </sst>
 </file>
@@ -384,12 +409,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="23">
@@ -639,7 +670,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -666,6 +697,54 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -681,24 +760,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -708,32 +769,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -744,45 +781,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -801,12 +799,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -824,6 +816,75 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1166,14 +1227,14 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A8" dT="2026-03-16T21:35:56.10" personId="{21BF80AD-7904-4FA1-8602-45F0B3EC668C}" id="{8DC31F13-F672-44C8-B6F9-D563EA730BE1}">
+  <threadedComment ref="A11" dT="2026-03-16T21:35:56.10" personId="{21BF80AD-7904-4FA1-8602-45F0B3EC668C}" id="{8DC31F13-F672-44C8-B6F9-D563EA730BE1}">
     <text>If we are adding search function</text>
   </threadedComment>
-  <threadedComment ref="A10" dT="2026-03-16T21:38:20.49" personId="{21BF80AD-7904-4FA1-8602-45F0B3EC668C}" id="{CD64EC9D-F2C7-4DD6-8F96-79671E574420}">
+  <threadedComment ref="A13" dT="2026-03-16T21:39:15.76" personId="{21BF80AD-7904-4FA1-8602-45F0B3EC668C}" id="{719EAB06-00FA-4EDC-8383-4E592611310C}">
+    <text>Here they can change password, name.</text>
+  </threadedComment>
+  <threadedComment ref="A15" dT="2026-03-16T21:38:20.49" personId="{21BF80AD-7904-4FA1-8602-45F0B3EC668C}" id="{CD64EC9D-F2C7-4DD6-8F96-79671E574420}">
     <text xml:space="preserve">I was thinking to make a ‘Gallery’ page. I will pull around 12 gardening images (3 x 4) and we could add that this would be ‘Instagram’ in ‘future development’ </text>
-  </threadedComment>
-  <threadedComment ref="A12" dT="2026-03-16T21:39:15.76" personId="{21BF80AD-7904-4FA1-8602-45F0B3EC668C}" id="{719EAB06-00FA-4EDC-8383-4E592611310C}">
-    <text>Here they can change password, name.</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -1221,6 +1282,256 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="79" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="10"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="82"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="84"/>
+      <c r="N2" s="12"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="11"/>
+      <c r="E3" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="N3" s="12"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="11"/>
+      <c r="N4" s="12"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="11"/>
+      <c r="F5" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="N5" s="12"/>
+    </row>
+    <row r="6" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="11"/>
+      <c r="N6" s="12"/>
+    </row>
+    <row r="7" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="11"/>
+      <c r="E7" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="44"/>
+      <c r="G7" s="45"/>
+      <c r="N7" s="12"/>
+    </row>
+    <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11"/>
+      <c r="N8" s="12"/>
+    </row>
+    <row r="9" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="11"/>
+      <c r="E9" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="27"/>
+      <c r="G9" s="28"/>
+      <c r="N9" s="12"/>
+    </row>
+    <row r="10" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="11"/>
+      <c r="N10" s="12"/>
+    </row>
+    <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="11"/>
+      <c r="E11" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="27"/>
+      <c r="G11" s="28"/>
+      <c r="N11" s="12"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="N12" s="12"/>
+    </row>
+    <row r="13" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="11"/>
+      <c r="N13" s="12"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="E14" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="30"/>
+      <c r="G14" s="31"/>
+      <c r="N14" s="12"/>
+    </row>
+    <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="11"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="34"/>
+      <c r="N15" s="12"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="11"/>
+      <c r="N16" s="12"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="11"/>
+      <c r="N17" s="12"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="11"/>
+      <c r="N18" s="12"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="11"/>
+      <c r="F19" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="12"/>
+    </row>
+    <row r="20" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="11"/>
+      <c r="N20" s="12"/>
+    </row>
+    <row r="21" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="11"/>
+      <c r="E21" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="27"/>
+      <c r="G21" s="28"/>
+      <c r="N21" s="12"/>
+    </row>
+    <row r="22" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="11"/>
+      <c r="N22" s="12"/>
+    </row>
+    <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="11"/>
+      <c r="E23" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="27"/>
+      <c r="G23" s="28"/>
+      <c r="N23" s="12"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="11"/>
+      <c r="N24" s="12"/>
+    </row>
+    <row r="25" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="11"/>
+      <c r="N25" s="12"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="11"/>
+      <c r="E26" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="30"/>
+      <c r="G26" s="31"/>
+      <c r="N26" s="12"/>
+    </row>
+    <row r="27" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="11"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="34"/>
+      <c r="N27" s="12"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="11"/>
+      <c r="N28" s="12"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="11"/>
+      <c r="N29" s="12"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="11"/>
+      <c r="N30" s="12"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="85" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="86"/>
+      <c r="C31" s="86"/>
+      <c r="D31" s="86"/>
+      <c r="E31" s="86"/>
+      <c r="F31" s="86"/>
+      <c r="G31" s="86"/>
+      <c r="H31" s="86"/>
+      <c r="I31" s="86"/>
+      <c r="J31" s="86"/>
+      <c r="K31" s="86"/>
+      <c r="N31" s="12"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="82"/>
+      <c r="B32" s="83"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="83"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="83"/>
+      <c r="G32" s="83"/>
+      <c r="H32" s="83"/>
+      <c r="I32" s="83"/>
+      <c r="J32" s="83"/>
+      <c r="K32" s="83"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:K2"/>
+    <mergeCell ref="A31:K32"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="E14:G15"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="E26:G27"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39184858-8DC0-4046-B941-100DAA15A86B}">
+  <dimension ref="A1:N41"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="9"/>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -1236,240 +1547,316 @@
       <c r="M1" s="15"/>
       <c r="N1" s="10"/>
     </row>
-    <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="11"/>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62" t="s">
+        <v>52</v>
+      </c>
       <c r="N2" s="12"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="3"/>
-      <c r="J3" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="N3" s="12"/>
+      <c r="A3" s="13"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="14"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="C4" s="4"/>
-      <c r="F4" s="5"/>
-      <c r="N4" s="12"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="10"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
-      <c r="C5" s="4"/>
-      <c r="F5" s="5"/>
-      <c r="K5" s="20" t="s">
-        <v>2</v>
-      </c>
+      <c r="E5" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="49"/>
       <c r="N5" s="12"/>
     </row>
-    <row r="6" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
-      <c r="C6" s="4"/>
-      <c r="F6" s="5"/>
       <c r="N6" s="12"/>
     </row>
-    <row r="7" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="11"/>
-      <c r="C7" s="4"/>
-      <c r="F7" s="5"/>
-      <c r="J7" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" s="34"/>
-      <c r="L7" s="35"/>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="24"/>
+      <c r="C7" s="25"/>
+      <c r="E7" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="52"/>
       <c r="N7" s="12"/>
     </row>
-    <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="24"/>
-      <c r="F8" s="5"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54"/>
+      <c r="K8" s="55"/>
       <c r="N8" s="12"/>
     </row>
-    <row r="9" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="11"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="5"/>
-      <c r="J9" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="37"/>
-      <c r="L9" s="38"/>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="25"/>
       <c r="N9" s="12"/>
     </row>
-    <row r="10" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="11"/>
-      <c r="C10" s="4"/>
-      <c r="F10" s="5"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="63"/>
+      <c r="K10" s="63"/>
       <c r="N10" s="12"/>
     </row>
-    <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
-      <c r="C11" s="4"/>
-      <c r="F11" s="5"/>
-      <c r="J11" s="36" t="s">
-        <v>5</v>
-      </c>
-      <c r="K11" s="37"/>
-      <c r="L11" s="38"/>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="25"/>
+      <c r="C11" s="17"/>
+      <c r="E11" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
+      <c r="J11" s="66"/>
+      <c r="K11" s="67"/>
       <c r="N11" s="12"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
-      <c r="C12" s="4"/>
-      <c r="F12" s="5"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="69"/>
+      <c r="K12" s="70"/>
       <c r="N12" s="12"/>
     </row>
-    <row r="13" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="C13" s="4"/>
-      <c r="F13" s="5"/>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="25"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="71" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="71"/>
+      <c r="K13" s="71"/>
       <c r="N13" s="12"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11"/>
-      <c r="C14" s="4"/>
-      <c r="F14" s="5"/>
-      <c r="J14" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="K14" s="28"/>
-      <c r="L14" s="29"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="63"/>
+      <c r="K14" s="63"/>
       <c r="N14" s="12"/>
     </row>
-    <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="11"/>
-      <c r="C15" s="4"/>
-      <c r="F15" s="5"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="32"/>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="25"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="73"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="63"/>
       <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="8"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="63"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="76"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="63"/>
+      <c r="K16" s="63"/>
       <c r="N16" s="12"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="64"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="63"/>
       <c r="N17" s="12"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
       <c r="N18" s="12"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
-      <c r="K19" s="21" t="s">
-        <v>8</v>
-      </c>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
       <c r="N19" s="12"/>
     </row>
-    <row r="20" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="11"/>
-      <c r="C20" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
+      <c r="E20" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="46"/>
+      <c r="K20" s="46"/>
       <c r="N20" s="12"/>
     </row>
-    <row r="21" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="11"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="J21" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="37"/>
-      <c r="L21" s="38"/>
+      <c r="E21" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="25"/>
       <c r="N21" s="12"/>
     </row>
-    <row r="22" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="11"/>
-      <c r="C22" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
       <c r="N22" s="12"/>
     </row>
-    <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="11"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="J23" s="36" t="s">
-        <v>5</v>
-      </c>
-      <c r="K23" s="37"/>
-      <c r="L23" s="38"/>
+      <c r="H23" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="I23" s="25"/>
+      <c r="J23" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K23" s="25"/>
       <c r="N23" s="12"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="11"/>
+      <c r="J24" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="K24" s="25"/>
       <c r="N24" s="12"/>
     </row>
-    <row r="25" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="11"/>
-      <c r="C25" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
       <c r="N25" s="12"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="11"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="J26" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="K26" s="28"/>
-      <c r="L26" s="29"/>
+      <c r="E26" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="24"/>
+      <c r="K26" s="25"/>
       <c r="N26" s="12"/>
     </row>
-    <row r="27" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="11"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="32"/>
       <c r="N27" s="12"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
+      <c r="H28" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="25"/>
+      <c r="J28" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K28" s="25"/>
       <c r="N28" s="12"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="11"/>
+      <c r="J29" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="K29" s="25"/>
       <c r="N29" s="12"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -1478,344 +1865,15 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="11"/>
-      <c r="N31" s="12"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="14"/>
-    </row>
-  </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="J21:L21"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="J26:L27"/>
-    <mergeCell ref="C20:F21"/>
-    <mergeCell ref="C22:F23"/>
-    <mergeCell ref="C25:F27"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="D8:E9"/>
-    <mergeCell ref="J14:L15"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="J9:L9"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39184858-8DC0-4046-B941-100DAA15A86B}">
-  <dimension ref="A1:N38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="10"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="11"/>
-      <c r="E2" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="47"/>
-      <c r="N2" s="12"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="N3" s="12"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="43"/>
-      <c r="E4" s="61" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="63"/>
-      <c r="N4" s="12"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="66"/>
-      <c r="N5" s="12"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="43"/>
-      <c r="N6" s="12"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="N7" s="12"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="43"/>
-      <c r="C8" s="17"/>
-      <c r="E8" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="50"/>
-      <c r="N8" s="12"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="52"/>
-      <c r="K9" s="53"/>
-      <c r="N9" s="12"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="43"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="54"/>
-      <c r="K10" s="54"/>
-      <c r="N10" s="12"/>
-    </row>
-    <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="N11" s="12"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="43"/>
-      <c r="G12" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="56"/>
-      <c r="I12" s="57"/>
-      <c r="N12" s="12"/>
-    </row>
-    <row r="13" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="60"/>
-      <c r="N13" s="12"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="N14" s="12"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="N15" s="12"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="N16" s="12"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="E17" s="67" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="67"/>
-      <c r="G17" s="67"/>
-      <c r="H17" s="67"/>
-      <c r="I17" s="67"/>
-      <c r="J17" s="67"/>
-      <c r="K17" s="67"/>
-      <c r="N17" s="12"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="E18" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="44"/>
-      <c r="K18" s="43"/>
-      <c r="N18" s="12"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="N19" s="12"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="H20" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="I20" s="43"/>
-      <c r="J20" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="K20" s="43"/>
-      <c r="N20" s="12"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="J21" s="42" t="s">
-        <v>12</v>
-      </c>
-      <c r="K21" s="43"/>
-      <c r="N21" s="12"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="N22" s="12"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="E23" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="44"/>
-      <c r="K23" s="43"/>
-      <c r="N23" s="12"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="N24" s="12"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
-      <c r="H25" s="42" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" s="43"/>
-      <c r="J25" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="K25" s="43"/>
-      <c r="N25" s="12"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="11"/>
-      <c r="J26" s="42" t="s">
-        <v>12</v>
-      </c>
-      <c r="K26" s="43"/>
-      <c r="N26" s="12"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="11"/>
-      <c r="N27" s="12"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="11"/>
-      <c r="E28" s="42" t="s">
+      <c r="E31" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="44"/>
-      <c r="K28" s="43"/>
-      <c r="N28" s="12"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="N29" s="12"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="11"/>
-      <c r="H30" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="I30" s="43"/>
-      <c r="J30" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="K30" s="43"/>
-      <c r="N30" s="12"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="11"/>
-      <c r="J31" s="42" t="s">
-        <v>12</v>
-      </c>
-      <c r="K31" s="43"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="25"/>
       <c r="N31" s="12"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -1824,39 +1882,39 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="11"/>
-      <c r="E33" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
-      <c r="H33" s="44"/>
-      <c r="I33" s="44"/>
-      <c r="J33" s="44"/>
-      <c r="K33" s="43"/>
+      <c r="H33" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="25"/>
+      <c r="J33" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K33" s="25"/>
       <c r="N33" s="12"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="11"/>
+      <c r="J34" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="K34" s="25"/>
       <c r="N34" s="12"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="11"/>
-      <c r="H35" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" s="43"/>
-      <c r="J35" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="K35" s="43"/>
       <c r="N35" s="12"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="11"/>
-      <c r="J36" s="42" t="s">
-        <v>12</v>
-      </c>
-      <c r="K36" s="43"/>
+      <c r="E36" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="24"/>
+      <c r="K36" s="25"/>
       <c r="N36" s="12"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
@@ -1864,50 +1922,73 @@
       <c r="N37" s="12"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18"/>
-      <c r="L38" s="18"/>
-      <c r="M38" s="18"/>
-      <c r="N38" s="14"/>
+      <c r="A38" s="11"/>
+      <c r="H38" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="25"/>
+      <c r="J38" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K38" s="25"/>
+      <c r="N38" s="12"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="11"/>
+      <c r="J39" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="K39" s="25"/>
+      <c r="N39" s="12"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="11"/>
+      <c r="N40" s="12"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="13"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18"/>
+      <c r="N41" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="E18:K18"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="E23:K23"/>
-    <mergeCell ref="E17:K17"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="E2:K2"/>
-    <mergeCell ref="E8:K9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="G12:I13"/>
-    <mergeCell ref="E4:K5"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="E28:K28"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="E33:K33"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="E31:K31"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="E36:K36"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="E5:K5"/>
+    <mergeCell ref="E11:K12"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="G15:I16"/>
+    <mergeCell ref="E7:K8"/>
+    <mergeCell ref="E21:K21"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="E26:K26"/>
+    <mergeCell ref="E20:K20"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A13:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -1934,7 +2015,9 @@
       <c r="F1" s="15"/>
       <c r="G1" s="15"/>
       <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
+      <c r="I1" s="15" t="s">
+        <v>52</v>
+      </c>
       <c r="J1" s="15"/>
       <c r="K1" s="15"/>
       <c r="L1" s="15"/>
@@ -1950,16 +2033,16 @@
       <c r="N3" s="12"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="43"/>
+      <c r="A4" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="24"/>
+      <c r="C4" s="25"/>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N4" s="12"/>
     </row>
@@ -1968,17 +2051,17 @@
       <c r="N5" s="12"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="43"/>
+      <c r="A6" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="25"/>
       <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="68"/>
+        <v>32</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="22"/>
       <c r="N6" s="12"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1986,16 +2069,16 @@
       <c r="N7" s="12"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="43"/>
+      <c r="A8" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="25"/>
       <c r="C8" s="17"/>
       <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="19" t="s">
         <v>35</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>36</v>
       </c>
       <c r="N8" s="12"/>
     </row>
@@ -2004,10 +2087,16 @@
       <c r="N9" s="12"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="43"/>
+      <c r="A10" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="25"/>
+      <c r="E10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="78" t="s">
+        <v>50</v>
+      </c>
       <c r="N10" s="12"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -2015,10 +2104,10 @@
       <c r="N11" s="12"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="43"/>
+      <c r="A12" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="25"/>
       <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -2031,10 +2120,26 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="11"/>
+      <c r="C15" s="79" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="81"/>
       <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="11"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="84"/>
       <c r="N16" s="12"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -2134,23 +2239,222 @@
       <c r="N37" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C15:I16"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F8" r:id="rId1" xr:uid="{AB0759F5-B436-4EC4-ABBD-3C96423C558C}"/>
+    <hyperlink ref="F10" r:id="rId2" xr:uid="{14CDA7AF-7185-4210-BF96-2B52A97A1932}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53280C7C-3FDA-4CC5-A80A-0ADCFBF12B94}">
+  <dimension ref="A1:J36"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="9"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="10"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="11"/>
+      <c r="B2" s="62" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="12"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="13"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="14"/>
+    </row>
+    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D5" s="1"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D6" s="4"/>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D7" s="4"/>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D8" s="4"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D9" s="4"/>
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D10" s="4"/>
+      <c r="E10" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="F10" s="40"/>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D11" s="4"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D12" s="4"/>
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D13" s="4"/>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D14" s="4"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D15" s="4"/>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D16" s="4"/>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D17" s="4"/>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="4:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D18" s="6"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="8"/>
+    </row>
+    <row r="22" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D22" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+    </row>
+    <row r="23" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+    </row>
+    <row r="24" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D24" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+    </row>
+    <row r="25" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+    </row>
+    <row r="27" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D27" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
+    </row>
+    <row r="28" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+    </row>
+    <row r="29" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
+    </row>
+    <row r="32" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="10"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="13"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="E10:F11"/>
+    <mergeCell ref="D22:G23"/>
+    <mergeCell ref="D24:G25"/>
+    <mergeCell ref="D27:G29"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA729801-4BBB-4D56-B2FD-D1C8269180A5}">
   <dimension ref="A1:N39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2179,19 +2483,19 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
-      <c r="G3" s="68" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
+      <c r="G3" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
       <c r="N3" s="12"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="43"/>
+      <c r="A4" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="24"/>
+      <c r="C4" s="25"/>
       <c r="N4" s="12"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -2199,63 +2503,63 @@
       <c r="N5" s="12"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="43"/>
-      <c r="E6" s="69" t="s">
+      <c r="A6" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="25"/>
+      <c r="E6" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="57"/>
+      <c r="H6" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="70"/>
-      <c r="H6" s="69" t="s">
+      <c r="I6" s="57"/>
+      <c r="K6" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="70"/>
-      <c r="K6" s="69" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6" s="70"/>
+      <c r="L6" s="57"/>
       <c r="N6" s="12"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="72"/>
-      <c r="H7" s="71"/>
-      <c r="I7" s="72"/>
-      <c r="K7" s="71"/>
-      <c r="L7" s="72"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="59"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="59"/>
+      <c r="K7" s="58"/>
+      <c r="L7" s="59"/>
       <c r="N7" s="12"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="43"/>
+      <c r="A8" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="25"/>
       <c r="C8" s="17"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="72"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="72"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="72"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="59"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="59"/>
+      <c r="K8" s="58"/>
+      <c r="L8" s="59"/>
       <c r="N8" s="12"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="74"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="74"/>
-      <c r="K9" s="73"/>
-      <c r="L9" s="74"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="61"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="61"/>
+      <c r="K9" s="60"/>
+      <c r="L9" s="61"/>
       <c r="N9" s="12"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="43"/>
+      <c r="A10" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="25"/>
       <c r="N10" s="12"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -2263,52 +2567,52 @@
       <c r="N11" s="12"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="43"/>
-      <c r="E12" s="69" t="s">
+      <c r="A12" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="25"/>
+      <c r="E12" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="57"/>
+      <c r="H12" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="70"/>
-      <c r="H12" s="69" t="s">
+      <c r="I12" s="57"/>
+      <c r="K12" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="I12" s="70"/>
-      <c r="K12" s="69" t="s">
-        <v>42</v>
-      </c>
-      <c r="L12" s="70"/>
+      <c r="L12" s="57"/>
       <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="11"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="72"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="72"/>
-      <c r="K13" s="71"/>
-      <c r="L13" s="72"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="59"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="59"/>
+      <c r="K13" s="58"/>
+      <c r="L13" s="59"/>
       <c r="N13" s="12"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="11"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="72"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="72"/>
-      <c r="K14" s="71"/>
-      <c r="L14" s="72"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="59"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="59"/>
+      <c r="K14" s="58"/>
+      <c r="L14" s="59"/>
       <c r="N14" s="12"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="11"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="74"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="74"/>
-      <c r="K15" s="73"/>
-      <c r="L15" s="74"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="61"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="61"/>
+      <c r="K15" s="60"/>
+      <c r="L15" s="61"/>
       <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -2321,48 +2625,48 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="E18" s="69" t="s">
+      <c r="E18" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="57"/>
+      <c r="H18" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="F18" s="70"/>
-      <c r="H18" s="69" t="s">
+      <c r="I18" s="57"/>
+      <c r="K18" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="I18" s="70"/>
-      <c r="K18" s="69" t="s">
-        <v>45</v>
-      </c>
-      <c r="L18" s="70"/>
+      <c r="L18" s="57"/>
       <c r="N18" s="12"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="72"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="72"/>
-      <c r="K19" s="71"/>
-      <c r="L19" s="72"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="59"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="59"/>
+      <c r="K19" s="58"/>
+      <c r="L19" s="59"/>
       <c r="N19" s="12"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="11"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="72"/>
-      <c r="H20" s="71"/>
-      <c r="I20" s="72"/>
-      <c r="K20" s="71"/>
-      <c r="L20" s="72"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="59"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="59"/>
+      <c r="K20" s="58"/>
+      <c r="L20" s="59"/>
       <c r="N20" s="12"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="11"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="74"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="74"/>
-      <c r="K21" s="73"/>
-      <c r="L21" s="74"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="61"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="61"/>
+      <c r="K21" s="60"/>
+      <c r="L21" s="61"/>
       <c r="N21" s="12"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -2451,11 +2755,9 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="E18:F21"/>
-    <mergeCell ref="H18:I21"/>
-    <mergeCell ref="K18:L21"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="K6:L9"/>
     <mergeCell ref="E12:F15"/>
     <mergeCell ref="H12:I15"/>
@@ -2463,9 +2765,11 @@
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="E6:F9"/>
     <mergeCell ref="H6:I9"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="E18:F21"/>
+    <mergeCell ref="H18:I21"/>
+    <mergeCell ref="K18:L21"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
